--- a/business_forms/038_investor_milestone_report_form--business_forms.xlsx
+++ b/business_forms/038_investor_milestone_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -850,12 +850,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>investor_signoff_comment</t>
+          <t>investor_signoff_comment_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Investor Signoff Comment</t>
+          <t>Investor Signoff Comment 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>signoff_status</t>
+          <t>signoff_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Signoff Status</t>
+          <t>Signoff Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Final Signoff Complete</t>
+          <t>Final Signoff Complete (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>signoff_status_choices</t>
+          <t>signoff_status_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>signoff_status_choices</t>
+          <t>signoff_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
